--- a/data/municipal_accident_totals_15y.xlsx
+++ b/data/municipal_accident_totals_15y.xlsx
@@ -436,662 +436,662 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bend | type=Accidents between vehicles</t>
+          <t>Motorway | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>Motorway | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>Motorway | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>Motorway | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>Motorway | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>Motorway | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>Motorway | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>Motorway | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>Motorway | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>Motorway | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>Motorway | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>Motorway | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>Motorway | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>Motorway | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>loc=Motorway | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>Motorway | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bend | type=Accidents between vehicles</t>
+          <t>Other roads | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>Other roads | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>Other roads | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Crossoroad | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Crossoroad | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Crossoroad | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Crossoroad | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Level crossing | type=Accidents between vehicles</t>
+          <t>Other roads | Level crossing | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Level crossing | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Level crossing | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Level crossing | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Level crossing | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>Other roads | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>Other roads | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Traffic circle | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Traffic circle | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>Other roads | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>Other roads | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>loc=Other roads | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>Other roads | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bend | type=Accidents between vehicles</t>
+          <t>Urban road | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>Urban road | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>Urban road | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Crossoroad | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Crossoroad | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Crossoroad | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Crossoroad | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Level crossing | type=Accidents between vehicles</t>
+          <t>Urban road | Level crossing | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Level crossing | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Level crossing | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Level crossing | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Level crossing | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>Urban road | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>Urban road | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Traffic circle | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Traffic circle | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>Urban road | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>Urban road | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>loc=Urban road | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>Urban road | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>city_total_15y</t>
+          <t>city_total</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bend | type=Accidents between vehicles</t>
+          <t>%Motorway | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>%Motorway | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>%Motorway | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>%Motorway | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>%Motorway | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>%Motorway | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>%Motorway | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>%Motorway | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>%Motorway | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>%Motorway | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>%Motorway | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>%Motorway | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>%Motorway | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>%Motorway | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Motorway | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>%Motorway | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bend | type=Accidents between vehicles</t>
+          <t>%Other roads | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>%Other roads | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>%Other roads | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Crossoroad | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Crossoroad | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Crossoroad | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Crossoroad | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Level crossing | type=Accidents between vehicles</t>
+          <t>%Other roads | Level crossing | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Level crossing | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Level crossing | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Level crossing | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Level crossing | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>%Other roads | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>%Other roads | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Traffic circle | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Traffic circle | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>%Other roads | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>%Other roads | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Other roads | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>%Other roads | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bend | type=Accidents between vehicles</t>
+          <t>%Urban road | Bend | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bend | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Bend | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bend | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Bend | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bump - slope - bottleneck | type=Accidents between vehicles</t>
+          <t>%Urban road | Bump - slope - bottleneck | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bump - slope - bottleneck | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Bump - slope - bottleneck | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Bump - slope - bottleneck | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Bump - slope - bottleneck | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Crossoroad | type=Accidents between vehicles</t>
+          <t>%Urban road | Crossoroad | Accidents between vehicles</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Crossoroad | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Crossoroad | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Crossoroad | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Crossoroad | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Level crossing | type=Accidents between vehicles</t>
+          <t>%Urban road | Level crossing | Accidents between vehicles</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Level crossing | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Level crossing | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Level crossing | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Level crossing | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Straight stretch | type=Accidents between vehicles</t>
+          <t>%Urban road | Straight stretch | Accidents between vehicles</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Straight stretch | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Straight stretch | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Straight stretch | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Straight stretch | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Traffic circle | type=Accidents between vehicles</t>
+          <t>%Urban road | Traffic circle | Accidents between vehicles</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Traffic circle | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Traffic circle | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Traffic circle | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Traffic circle | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Tunnel | type=Accidents between vehicles</t>
+          <t>%Urban road | Tunnel | Accidents between vehicles</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Tunnel | type=Accidents involving a single vehicle</t>
+          <t>%Urban road | Tunnel | Accidents involving a single vehicle</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>%loc=Urban road | intersection=Tunnel | type=Vehicle-pedestrian accident</t>
+          <t>%Urban road | Tunnel | Vehicle-pedestrian accident</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>avg_bus_or_trolley_bus_15y</t>
+          <t>avg bus or trolley bus</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>avg_motor_cars_15y</t>
+          <t>avg motor cars</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>avg_motor_units_15y</t>
+          <t>avg motor units</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>avg_motorcycles_15y</t>
+          <t>avg motorcycles</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>avg_other_vehicles_15y</t>
+          <t>avg other vehicles</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>avg_three_wheeler_or_motor_van_15y</t>
+          <t>avg three wheeler or motor van</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>avg_trailer_15y</t>
+          <t>avg trailer</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>avg_trucks_15y</t>
+          <t>avg trucks</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
-          <t>avg_total_vehicles_15y</t>
+          <t>avg total vehicles</t>
         </is>
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
-          <t>%avg_bus_or_trolley_bus_15y</t>
+          <t>pct bus or trolley bus</t>
         </is>
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
-          <t>%avg_motor_cars_15y</t>
+          <t>pct motor cars</t>
         </is>
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
-          <t>%avg_motor_units_15y</t>
+          <t>pct motor units</t>
         </is>
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
-          <t>%avg_motorcycles_15y</t>
+          <t>pct motorcycles</t>
         </is>
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
-          <t>%avg_other_vehicles_15y</t>
+          <t>pct other vehicles</t>
         </is>
       </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
-          <t>%avg_three_wheeler_or_motor_van_15y</t>
+          <t>pct three wheeler or motor van</t>
         </is>
       </c>
       <c r="EB1" s="1" t="inlineStr">
         <is>
-          <t>%avg_trailer_15y</t>
+          <t>pct trailer</t>
         </is>
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
-          <t>%avg_trucks_15y</t>
+          <t>pct trucks</t>
         </is>
       </c>
     </row>
